--- a/data/trans_camb/P15A-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P15A-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,11</t>
+          <t>-1,66; 3,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,84</t>
+          <t>-2,68; 1,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 0,0</t>
+          <t>-3,72; -0,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 2,97</t>
+          <t>-2,49; 3,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 1,45</t>
+          <t>-3,35; 1,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,86</t>
+          <t>-2,62; 1,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 2,17</t>
+          <t>-1,48; 2,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,97</t>
+          <t>-2,16; 1,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 0,4</t>
+          <t>-2,25; 0,5</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-48,53; 182,44</t>
+          <t>-49,02; 187,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-72,86; 115,34</t>
+          <t>-73,31; 99,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-88,06; 36,77</t>
+          <t>-90,22; 3,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-71,04; 249,96</t>
+          <t>-74,92; 235,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-80,66; 121,6</t>
+          <t>-79,64; 115,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,36; 152,98</t>
+          <t>-58,45; 181,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,9; 120,26</t>
+          <t>-45,16; 119,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,75; 52,07</t>
+          <t>-63,25; 67,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-65,27; 25,18</t>
+          <t>-62,09; 32,68</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,66</t>
+          <t>-3,57; 1,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 0,1</t>
+          <t>-4,5; 0,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1,83</t>
+          <t>-3,67; 1,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 1,54</t>
+          <t>-2,21; 1,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 4,53</t>
+          <t>-0,48; 4,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,27</t>
+          <t>-2,17; 1,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 1,09</t>
+          <t>-2,12; 1,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,57</t>
+          <t>-1,68; 1,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,22</t>
+          <t>-2,18; 0,95</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-69,86; 89,58</t>
+          <t>-68,52; 91,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-87,02; 17,8</t>
+          <t>-87,58; 15,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,96; 109,36</t>
+          <t>-72,0; 93,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 389,96</t>
+          <t>-100,0; 386,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,94; 706,51</t>
+          <t>-36,55; 666,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-76,79; 226,41</t>
+          <t>-77,04; 217,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,2; 68,4</t>
+          <t>-61,13; 63,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,12; 92,82</t>
+          <t>-49,44; 91,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-62,13; 76,47</t>
+          <t>-61,48; 59,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,93; -0,21</t>
+          <t>-5,08; -0,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,76; -1,14</t>
+          <t>-5,9; -1,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,1; -1,06</t>
+          <t>-6,53; -0,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 2,09</t>
+          <t>-4,29; 2,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 5,27</t>
+          <t>-2,74; 5,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 2,93</t>
+          <t>-3,74; 2,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,04; -0,19</t>
+          <t>-4,29; -0,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,55; -0,34</t>
+          <t>-4,41; -0,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,04; -0,39</t>
+          <t>-5,28; -0,77</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,89; -1,74</t>
+          <t>-74,96; -3,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-83,14; -24,15</t>
+          <t>-82,88; -25,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-91,85; -25,99</t>
+          <t>-89,49; -20,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-88,67; 185,2</t>
+          <t>-88,69; 199,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-77,98; 388,92</t>
+          <t>-69,98; 431,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,59; 266,14</t>
+          <t>-68,16; 232,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-69,7; -1,85</t>
+          <t>-70,25; -4,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,13; -4,11</t>
+          <t>-73,59; -3,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-82,79; -13,34</t>
+          <t>-82,4; -21,32</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,38</t>
+          <t>-1,49; 1,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 0,36</t>
+          <t>-2,2; 0,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,46</t>
+          <t>-2,26; 0,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,53</t>
+          <t>-3,09; 0,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; -0,88</t>
+          <t>-3,92; -0,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; -0,06</t>
+          <t>-3,51; 0,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,45</t>
+          <t>-1,66; 0,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,54; -0,45</t>
+          <t>-2,57; -0,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; -0,12</t>
+          <t>-2,23; -0,15</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,38; 62,01</t>
+          <t>-39,45; 54,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-56,98; 15,74</t>
+          <t>-56,29; 16,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,4; 20,76</t>
+          <t>-58,53; 14,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-69,94; 23,88</t>
+          <t>-67,5; 21,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-87,55; -25,09</t>
+          <t>-86,08; -27,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-75,27; -2,17</t>
+          <t>-74,25; 1,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 18,01</t>
+          <t>-43,6; 21,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-65,92; -16,54</t>
+          <t>-65,36; -19,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,63; -4,16</t>
+          <t>-58,85; -4,45</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 1,51</t>
+          <t>-3,34; 1,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 2,64</t>
+          <t>-2,5; 2,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 3,14</t>
+          <t>-2,53; 3,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,44</t>
+          <t>-2,77; 1,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,05</t>
+          <t>-3,19; 1,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 1,4</t>
+          <t>-2,66; 1,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,85</t>
+          <t>-2,38; 0,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,14</t>
+          <t>-2,2; 1,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,42</t>
+          <t>-1,92; 1,46</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-68,84; 80,22</t>
+          <t>-65,29; 88,51</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,68; 121,28</t>
+          <t>-48,46; 115,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-60,71; 144,63</t>
+          <t>-54,89; 181,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-50,75; 58,7</t>
+          <t>-50,29; 58,86</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-58,62; 42,81</t>
+          <t>-58,17; 48,34</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-50,25; 52,94</t>
+          <t>-49,86; 54,45</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-50,14; 30,8</t>
+          <t>-48,9; 30,78</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,13; 41,5</t>
+          <t>-44,88; 38,28</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-42,06; 49,41</t>
+          <t>-40,03; 51,62</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,47; -0,07</t>
+          <t>-6,21; 0,5</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 3,78</t>
+          <t>-4,19; 3,43</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,75; -0,97</t>
+          <t>-7,56; -1,17</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 2,62</t>
+          <t>-0,2; 2,65</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,78</t>
+          <t>-0,83; 1,93</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,9</t>
+          <t>-0,79; 2,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,7</t>
+          <t>-0,81; 1,66</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,77</t>
+          <t>-0,84; 1,89</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,68</t>
+          <t>-1,76; 0,72</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-83,56; 14,67</t>
+          <t>-84,04; 26,05</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-57,52; 106,68</t>
+          <t>-60,79; 94,8</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 19,19</t>
+          <t>-100,0; 34,37</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 159,59</t>
+          <t>-7,62; 155,58</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-29,8; 112,2</t>
+          <t>-28,68; 122,19</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 113,19</t>
+          <t>-28,55; 121,38</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-27,04; 73,76</t>
+          <t>-24,98; 72,45</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-26,67; 78,0</t>
+          <t>-25,31; 82,71</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-52,18; 29,93</t>
+          <t>-52,2; 31,83</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,05</t>
+          <t>-1,81; -0,05</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,98; -0,12</t>
+          <t>-2,03; -0,28</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,56; -0,63</t>
+          <t>-2,61; -0,73</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,82</t>
+          <t>-0,82; 0,83</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,51</t>
+          <t>-1,05; 0,5</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,47</t>
+          <t>-1,04; 0,53</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,22</t>
+          <t>-1,01; 0,21</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,26; -0,08</t>
+          <t>-1,27; -0,11</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,49; -0,25</t>
+          <t>-1,5; -0,24</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-41,75; 3,1</t>
+          <t>-42,3; -1,44</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-47,57; -3,93</t>
+          <t>-48,19; -7,83</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-60,32; -18,25</t>
+          <t>-61,77; -22,6</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-26,55; 34,84</t>
+          <t>-25,79; 35,15</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-34,79; 22,22</t>
+          <t>-33,23; 21,68</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-36,16; 20,11</t>
+          <t>-32,64; 22,11</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-27,3; 7,87</t>
+          <t>-27,93; 7,11</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-35,16; -2,75</t>
+          <t>-35,51; -3,79</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-42,22; -9,01</t>
+          <t>-42,41; -8,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P15A-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P15A-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,64</t>
+          <t>-1,56</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,84</t>
+          <t>-0,64</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,12</t>
+          <t>-1,66; 3,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 1,63</t>
+          <t>-2,69; 1,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,72; -0,22</t>
+          <t>-3,57; 0,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 3,38</t>
+          <t>-2,46; 3,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 1,41</t>
+          <t>-3,06; 1,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 1,95</t>
+          <t>-1,98; 2,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 2,27</t>
+          <t>-1,44; 2,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,03</t>
+          <t>-2,12; 1,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,5</t>
+          <t>-2,18; 0,63</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-61,76%</t>
+          <t>-58,58%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-32,26%</t>
+          <t>-24,73%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-49,02; 187,46</t>
+          <t>-50,88; 181,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-73,31; 99,88</t>
+          <t>-70,52; 121,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-90,22; 3,91</t>
+          <t>-87,96; 20,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-74,92; 235,43</t>
+          <t>-72,36; 269,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,64; 115,31</t>
+          <t>-78,69; 148,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,45; 181,78</t>
+          <t>-47,33; 198,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,16; 119,42</t>
+          <t>-45,03; 124,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,25; 67,62</t>
+          <t>-64,81; 57,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-62,09; 32,68</t>
+          <t>-58,54; 34,07</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,03</t>
+          <t>-0,98</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,51</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,78</t>
+          <t>-3,85; 1,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 0,08</t>
+          <t>-4,93; 0,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 1,71</t>
+          <t>-3,89; 1,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,63</t>
+          <t>-2,05; 1,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 4,22</t>
+          <t>-0,28; 4,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,18</t>
+          <t>-1,83; 1,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,07</t>
+          <t>-2,13; 1,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 1,62</t>
+          <t>-1,72; 1,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,95</t>
+          <t>-2,14; 1,2</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-28,38%</t>
+          <t>-26,96%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-11,6%</t>
+          <t>-9,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-21,18%</t>
+          <t>-19,87%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-68,52; 91,15</t>
+          <t>-72,23; 81,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-87,58; 15,6</t>
+          <t>-86,7; 18,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,0; 93,64</t>
+          <t>-73,8; 78,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 386,7</t>
+          <t>-100,0; 348,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,55; 666,9</t>
+          <t>-24,1; 698,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-77,04; 217,91</t>
+          <t>-69,73; 316,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,13; 63,11</t>
+          <t>-60,99; 69,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,44; 91,95</t>
+          <t>-51,66; 102,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-61,48; 59,28</t>
+          <t>-61,0; 76,73</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,36</t>
+          <t>-2,08</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>-0,0</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,57</t>
+          <t>-1,6</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,08; -0,39</t>
+          <t>-4,97; -0,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -1,23</t>
+          <t>-5,93; -1,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,53; -0,95</t>
+          <t>-4,76; 0,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 2,05</t>
+          <t>-4,22; 2,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 5,53</t>
+          <t>-2,3; 6,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 2,92</t>
+          <t>-3,59; 2,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; -0,38</t>
+          <t>-4,37; -0,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,41; -0,38</t>
+          <t>-4,45; -0,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,28; -0,77</t>
+          <t>-3,78; 0,51</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-64,5%</t>
+          <t>-39,91%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>-0,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-54,96%</t>
+          <t>-34,15%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-74,96; -3,84</t>
+          <t>-74,12; -4,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-82,88; -25,38</t>
+          <t>-85,04; -21,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-89,49; -20,93</t>
+          <t>-71,55; 19,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-88,69; 199,11</t>
+          <t>-83,88; 286,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,98; 431,95</t>
+          <t>-60,81; 671,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,16; 232,62</t>
+          <t>-76,72; 184,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-70,25; -4,64</t>
+          <t>-70,96; -7,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-73,59; -3,36</t>
+          <t>-73,17; -5,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-82,4; -21,32</t>
+          <t>-64,92; 16,76</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,91</t>
+          <t>-0,75</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-0,86</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,35</t>
+          <t>-1,55; 1,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,4</t>
+          <t>-2,43; 0,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,34</t>
+          <t>-2,1; 0,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,38</t>
+          <t>-3,09; 0,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,92; -0,77</t>
+          <t>-4,0; -0,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 0,02</t>
+          <t>-2,72; 0,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,58</t>
+          <t>-1,62; 0,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; -0,53</t>
+          <t>-2,46; -0,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; -0,15</t>
+          <t>-2,01; 0,15</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-28,9%</t>
+          <t>-23,84%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-43,72%</t>
+          <t>-30,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-35,67%</t>
+          <t>-26,17%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,45; 54,98</t>
+          <t>-41,04; 52,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-56,29; 16,52</t>
+          <t>-60,6; 13,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,53; 14,07</t>
+          <t>-55,5; 22,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-67,5; 21,03</t>
+          <t>-68,21; 11,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-86,08; -27,97</t>
+          <t>-87,12; -27,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-74,25; 1,38</t>
+          <t>-59,37; 21,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-43,6; 21,39</t>
+          <t>-42,11; 17,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-65,36; -19,18</t>
+          <t>-64,73; -17,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,85; -4,45</t>
+          <t>-51,23; 6,17</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,48</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,31</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 1,58</t>
+          <t>-3,54; 1,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 2,49</t>
+          <t>-2,44; 2,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 3,47</t>
+          <t>-3,15; 2,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,56</t>
+          <t>-2,59; 1,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 1,11</t>
+          <t>-2,99; 0,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 1,48</t>
+          <t>-2,32; 1,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 0,86</t>
+          <t>-2,41; 0,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,07</t>
+          <t>-2,3; 1,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,46</t>
+          <t>-1,87; 1,45</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>-10,84%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-12,23%</t>
+          <t>-6,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-7,13%</t>
+          <t>-8,15%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,29; 88,51</t>
+          <t>-68,1; 78,09</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,46; 115,36</t>
+          <t>-44,73; 129,1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,89; 181,37</t>
+          <t>-63,57; 107,25</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-50,29; 58,86</t>
+          <t>-50,8; 51,65</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-58,17; 48,34</t>
+          <t>-58,93; 36,75</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-49,86; 54,45</t>
+          <t>-45,05; 67,66</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-48,9; 30,78</t>
+          <t>-50,84; 29,89</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-44,88; 38,28</t>
+          <t>-44,73; 36,19</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 51,62</t>
+          <t>-39,04; 53,79</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-4,48</t>
+          <t>-4,37</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-0,72</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 0,5</t>
+          <t>-6,08; 0,17</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 3,43</t>
+          <t>-4,32; 3,45</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,56; -1,17</t>
+          <t>-7,7; -0,84</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,65</t>
+          <t>-0,15; 2,52</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,93</t>
+          <t>-0,59; 1,98</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,0</t>
+          <t>-1,02; 1,52</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,66</t>
+          <t>-0,87; 1,68</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,89</t>
+          <t>-0,89; 1,79</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,72</t>
+          <t>-1,81; 0,7</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-82,54%</t>
+          <t>-80,53%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-21,17%</t>
+          <t>-25,3%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-84,04; 26,05</t>
+          <t>-83,27; 14,07</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-60,79; 94,8</t>
+          <t>-60,08; 104,68</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 34,37</t>
+          <t>-100,0; 34,9</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 155,58</t>
+          <t>-6,63; 161,5</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 122,19</t>
+          <t>-23,18; 121,81</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-28,55; 121,38</t>
+          <t>-36,02; 92,1</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 72,45</t>
+          <t>-25,94; 72,75</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-25,31; 82,71</t>
+          <t>-26,72; 79,17</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-52,2; 31,83</t>
+          <t>-53,52; 34,44</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1,59</t>
+          <t>-1,36</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,9</t>
+          <t>-0,71</t>
         </is>
       </c>
     </row>
@@ -1973,22 +1973,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,81; -0,05</t>
+          <t>-1,95; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,03; -0,28</t>
+          <t>-2,02; -0,3</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,61; -0,73</t>
+          <t>-2,4; -0,57</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,83</t>
+          <t>-0,87; 0,76</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1998,22 +1998,22 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,53</t>
+          <t>-0,87; 0,64</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,21</t>
+          <t>-0,98; 0,11</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,27; -0,11</t>
+          <t>-1,27; -0,12</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,5; -0,24</t>
+          <t>-1,31; -0,1</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-42,67%</t>
+          <t>-36,51%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-8,67%</t>
+          <t>-2,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-27,81%</t>
+          <t>-21,81%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-42,3; -1,44</t>
+          <t>-44,25; 0,66</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-48,19; -7,83</t>
+          <t>-46,95; -8,72</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-61,77; -22,6</t>
+          <t>-54,57; -14,41</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 35,15</t>
+          <t>-26,87; 31,48</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-33,23; 21,68</t>
+          <t>-34,34; 20,89</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-32,64; 22,11</t>
+          <t>-27,33; 27,98</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-27,93; 7,11</t>
+          <t>-27,94; 4,08</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-35,51; -3,79</t>
+          <t>-36,0; -3,68</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-42,41; -8,61</t>
+          <t>-36,75; -3,74</t>
         </is>
       </c>
     </row>
